--- a/examples/jpetstore-6/.understand-anything/doc-output/si-실적요약보고서.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-실적요약보고서.xlsx
@@ -110,7 +110,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>382ee31ae008b21bc32097fd195caa9802aeda36</t>
+          <t>[미확인]</t>
         </is>
       </c>
     </row>
@@ -194,7 +194,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>최근 2주 (2026-06-21T10:53:30.000Z ~ 2026-07-05T10:53:30.000Z] — 앵커 = HEAD 커밋 시각(벽시계 아님)</t>
+          <t>최근 2주 (2026-06-22T02:00:44.000Z ~ 2026-07-06T02:00:44.000Z] — 앵커 = HEAD 커밋 시각(벽시계 아님)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -212,7 +212,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>커밋 12건(작성자 1명, 머지 0건), 파일 154개 변경(+12334/−1) · 생성물/산출물 별도 58개(+43929/−551) — 실적 아님</t>
+          <t>커밋 13건(작성자 1명, 머지 0건), 파일 154개 변경(+12334/−1) · 생성물/산출물 별도 60개(+44027/−551) — 실적 아님</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -248,7 +248,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>커밋 0→12(+12) · 실적 라인 0→12335(+12335) — 직전 (2026-06-07T10:53:30.000Z ~ 2026-06-21T10:53:30.000Z]</t>
+          <t>커밋 0→13(+13) · 실적 라인 0→12335(+12335) — 직전 (2026-06-08T02:00:44.000Z ~ 2026-06-22T02:00:44.000Z]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -594,12 +594,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>d7074bc0</t>
+          <t>41614a0e</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-05T03:53:41+09:00</t>
+          <t>2026-07-05T20:02:03+09:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -609,18 +609,18 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>fix(w5): 적대적 리뷰 반영 — 안정 시나리오 id·확정 스냅샷 박제·R7 복원 계약·QA 정밀화</t>
+          <t>fix(w6b): 리뷰 반영 — 구버전 산출물 크래시 가드·스키마 검증 degrade·월간 괄호·전월 rawArg 롤오버 + jpetstore 실적문서 벤더링</t>
         </is>
       </c>
       <c r="F2"/>
       <c r="G2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H2">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="I2">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -629,7 +629,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>.understand-anything/doc-output/rtm.xlsx, .understand-anything/doc-output/si-단위테스트시나리오.md, .understand-anything/doc-output/si-단위테스트시나리오.xlsx</t>
+          <t>.understand-anything/doc-output/si-실적요약보고서.md, .understand-anything/doc-output/si-실적요약보고서.xlsx</t>
         </is>
       </c>
     </row>
@@ -639,12 +639,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>678cdff9</t>
+          <t>d7074bc0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-05T03:33:07+09:00</t>
+          <t>2026-07-05T03:53:41+09:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -654,18 +654,18 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>feat(w5): 대시보드 시험 탭·R7 사용자 필드·R6 시각QA(P6-d~e)</t>
+          <t>fix(w5): 적대적 리뷰 반영 — 안정 시나리오 id·확정 스냅샷 박제·R7 복원 계약·QA 정밀화</t>
         </is>
       </c>
       <c r="F3"/>
       <c r="G3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>169</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>.gitignore</t>
+          <t>.understand-anything/doc-output/rtm.xlsx, .understand-anything/doc-output/si-단위테스트시나리오.md, .understand-anything/doc-output/si-단위테스트시나리오.xlsx</t>
         </is>
       </c>
     </row>
@@ -684,12 +684,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6e7301ca</t>
+          <t>678cdff9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-05T03:32:50+09:00</t>
+          <t>2026-07-05T03:33:07+09:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -699,18 +699,18 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>feat(w5): RTM 테스트 시나리오 엔진+산출물(P6-b~c) — testScenarios[]·si-단위테스트시나리오·rtm.xlsx 5시트</t>
+          <t>feat(w5): 대시보드 시험 탭·R7 사용자 필드·R6 시각QA(P6-d~e)</t>
         </is>
       </c>
       <c r="F4"/>
       <c r="G4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>1838</v>
+        <v>2</v>
       </c>
       <c r="I4">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>.understand-anything/doc-output/rtm.xlsx, .understand-anything/doc-output/si-단위테스트시나리오.md, .understand-anything/doc-output/si-단위테스트시나리오.xlsx</t>
+          <t>.gitignore</t>
         </is>
       </c>
     </row>
@@ -729,12 +729,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34df3f75</t>
+          <t>6e7301ca</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-07-05T02:47:49+09:00</t>
+          <t>2026-07-05T03:32:50+09:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -744,18 +744,18 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>fix(w4): 적대적 리뷰 반영 — 상대밴드 등급·무분산 제외·미도달 비점수화·행 신뢰도·shallow 감지</t>
+          <t>feat(w5): RTM 테스트 시나리오 엔진+산출물(P6-b~c) — testScenarios[]·si-단위테스트시나리오·rtm.xlsx 5시트</t>
         </is>
       </c>
       <c r="F5"/>
       <c r="G5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H5">
-        <v>46</v>
+        <v>1838</v>
       </c>
       <c r="I5">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>.understand-anything/doc-output/si-위험모듈리포트.md, .understand-anything/doc-output/si-위험모듈리포트.xlsx</t>
+          <t>.understand-anything/doc-output/rtm.xlsx, .understand-anything/doc-output/si-단위테스트시나리오.md, .understand-anything/doc-output/si-단위테스트시나리오.xlsx</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>c64558ef</t>
+          <t>34df3f75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-07-05T01:17:21+09:00</t>
+          <t>2026-07-05T02:47:49+09:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>feat(w4): 위험 모듈 리포트(P5-b~d) — risk-report.json·si-위험모듈리포트·xlsx 병기</t>
+          <t>fix(w4): 적대적 리뷰 반영 — 상대밴드 등급·무분산 제외·미도달 비점수화·행 신뢰도·shallow 감지</t>
         </is>
       </c>
       <c r="F6"/>
@@ -797,10 +797,10 @@
         <v>2</v>
       </c>
       <c r="H6">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -819,12 +819,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7eb428df</t>
+          <t>c64558ef</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-07-05T01:16:16+09:00</t>
+          <t>2026-07-05T01:17:21+09:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -834,18 +834,18 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>fix(w3): 매퍼 XML 오분류 — 부분 문자열 → 루트 요소 판별(isMapperXmlDocument)</t>
+          <t>feat(w4): 위험 모듈 리포트(P5-b~d) — risk-report.json·si-위험모듈리포트·xlsx 병기</t>
         </is>
       </c>
       <c r="F7"/>
       <c r="G7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="I7">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -854,7 +854,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>.understand-anything/doc-output/07_crud-matrix.md, .understand-anything/doc-output/07_crud-matrix.xlsx, .understand-anything/doc-output/si-프로그램목록.md</t>
+          <t>.understand-anything/doc-output/si-위험모듈리포트.md, .understand-anything/doc-output/si-위험모듈리포트.xlsx</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>e31bb89b</t>
+          <t>7eb428df</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-05T00:33:26+09:00</t>
+          <t>2026-07-05T01:16:16+09:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -879,18 +879,18 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>fix(w7): 적대적 리뷰 반영 — 문서정보 표지·검증 스파인·stale 경고·서식·라이터 견고화</t>
+          <t>fix(w3): 매퍼 XML 오분류 — 부분 문자열 → 루트 요소 판별(isMapperXmlDocument)</t>
         </is>
       </c>
       <c r="F8"/>
       <c r="G8">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>.understand-anything/doc-output/06_program-list.xlsx, .understand-anything/doc-output/07_crud-matrix.xlsx, .understand-anything/doc-output/08_batch-list.xlsx</t>
+          <t>.understand-anything/doc-output/07_crud-matrix.md, .understand-anything/doc-output/07_crud-matrix.xlsx, .understand-anything/doc-output/si-프로그램목록.md</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>c012eae7</t>
+          <t>e31bb89b</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-07-05T00:19:56+09:00</t>
+          <t>2026-07-05T00:33:26+09:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>feat(w7): xlsx 내보내기(P4-a~c) — zero-dep 결정론 라이터·문서/RTM 병기·대시보드 다운로드</t>
+          <t>fix(w7): 적대적 리뷰 반영 — 문서정보 표지·검증 스파인·stale 경고·서식·라이터 견고화</t>
         </is>
       </c>
       <c r="F9"/>
@@ -954,12 +954,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>a49d9fd0</t>
+          <t>c012eae7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-07-04T22:44:39+09:00</t>
+          <t>2026-07-05T00:19:56+09:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -969,18 +969,18 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>feat(w3): 테스트 유형 분리 + demo 데이터 재생성(W1~W3 반영)</t>
+          <t>feat(w7): xlsx 내보내기(P4-a~c) — zero-dep 결정론 라이터·문서/RTM 병기·대시보드 다운로드</t>
         </is>
       </c>
       <c r="F10"/>
       <c r="G10">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H10">
-        <v>332</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>.understand-anything/doc-output/01_tech-stack.md, .understand-anything/doc-output/02_architecture.md, .understand-anything/doc-output/06_program-list.md</t>
+          <t>.understand-anything/doc-output/06_program-list.xlsx, .understand-anything/doc-output/07_crud-matrix.xlsx, .understand-anything/doc-output/08_batch-list.xlsx</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>c13ae0cf</t>
+          <t>a49d9fd0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-07-03T20:21:25+09:00</t>
+          <t>2026-07-04T22:44:39+09:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1014,18 +1014,18 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>feat(screens): S5 데모 데이터 — examples/jpetstore-6 화면설계서 22화면 벤더링 + sync</t>
+          <t>feat(w3): 테스트 유형 분리 + demo 데이터 재생성(W1~W3 반영)</t>
         </is>
       </c>
       <c r="F11"/>
       <c r="G11">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="H11">
-        <v>13294</v>
+        <v>332</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>.understand-anything/screen-overrides.json, .understand-anything/screens.json, .understand-anything/screens/actions_Account.action__editAccountForm.png</t>
+          <t>.understand-anything/doc-output/01_tech-stack.md, .understand-anything/doc-output/02_architecture.md, .understand-anything/doc-output/06_program-list.md</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>a5958109</t>
+          <t>c13ae0cf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-06-30T15:22:23+09:00</t>
+          <t>2026-07-03T20:21:25+09:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1059,18 +1059,18 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>chore(demo): jpetstore RTM 인테이크 데이터 갱신(이전 세션 미커밋 잔여)</t>
+          <t>feat(screens): S5 데모 데이터 — examples/jpetstore-6 화면설계서 22화면 벤더링 + sync</t>
         </is>
       </c>
       <c r="F12"/>
       <c r="G12">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="H12">
-        <v>969</v>
+        <v>13294</v>
       </c>
       <c r="I12">
-        <v>217</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>.understand-anything/rtm-requirements.json, .understand-anything/rtm.json</t>
+          <t>.understand-anything/screen-overrides.json, .understand-anything/screens.json, .understand-anything/screens/actions_Account.action__editAccountForm.png</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>dd798816</t>
+          <t>a5958109</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-06-24T14:46:25+09:00</t>
+          <t>2026-06-30T15:22:23+09:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1104,32 +1104,77 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>feat(demo): jpetstore-6 프로젝트를 examples/ 에 vendoring — 데모 단일소스화 + RTM 탭 데모 동작</t>
+          <t>chore(demo): jpetstore RTM 인테이크 데이터 갱신(이전 세션 미커밋 잔여)</t>
         </is>
       </c>
       <c r="F13"/>
       <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>969</v>
+      </c>
+      <c r="I13">
+        <v>217</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>.understand-anything/rtm-requirements.json, .understand-anything/rtm.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dd798816</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-24T14:46:25+09:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jun_kyung.lee</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>feat(demo): jpetstore-6 프로젝트를 examples/ 에 vendoring — 데모 단일소스화 + RTM 탭 데모 동작</t>
+        </is>
+      </c>
+      <c r="F14"/>
+      <c r="G14">
         <v>172</v>
       </c>
-      <c r="H13">
+      <c r="H14">
         <v>39536</v>
       </c>
-      <c r="I13">
+      <c r="I14">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>[확정]</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>[확정]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>.gitattributes, .gitignore, .mvn/extensions.xml</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K13"/>
+  <autoFilter ref="A1:K14"/>
 </worksheet>
 </file>
 

--- a/examples/jpetstore-6/.understand-anything/doc-output/si-실적요약보고서.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-실적요약보고서.xlsx
@@ -110,7 +110,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[미확인]</t>
+          <t>dfbb9822f7c17f41a39e96704f4ea4f455580278</t>
         </is>
       </c>
     </row>

--- a/examples/jpetstore-6/.understand-anything/doc-output/si-실적요약보고서.xlsx
+++ b/examples/jpetstore-6/.understand-anything/doc-output/si-실적요약보고서.xlsx
@@ -110,7 +110,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>df7e6586febd05eb320c391f26b36b878b24111f</t>
+          <t>a73a85b4dc02c36b56a65d9a79f6cd45b350a700</t>
         </is>
       </c>
     </row>
